--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.64.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.64.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -859,7 +859,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.64.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.64.xlsx
@@ -422,18 +422,18 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
-    <col width="27" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
-    <col width="50" customWidth="1" min="14" max="14"/>
-    <col width="51" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.64.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.64.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0064.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0064.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -607,14 +607,22 @@
           <t>L36: suspicious token(s): to2 (letter/digit mix) | localized OCR phrase divergence vs other OCR: "to 12th March" vs "to2" :: Letter of Defendant to2</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr"/>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>L54: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA | isolated marker/symbol line :: r ，</t>
+        </is>
+      </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L41: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | abbreviation/spacing may be garbled :: E.F. â€¢ &gt;</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]57</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]57</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L31: symbol-only separator/garbage line :: 1850.</t>
@@ -622,7 +630,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L49: isolated marker/symbol line :: P</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]57</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -642,7 +650,7 @@
       </c>
       <c r="W2" s="1" t="inlineStr">
         <is>
-          <t>L41: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | abbreviation/spacing may be garbled :: E.F. â€¢ &gt;</t>
+          <t>L41: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | abbreviation/spacing may be garbled :: E.F. • &gt;</t>
         </is>
       </c>
       <c r="X2" s="1" t="inlineStr"/>
@@ -661,7 +669,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>96</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -670,10 +678,14 @@
       <c r="G3" s="1" t="inlineStr"/>
       <c r="H3" s="1" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr"/>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
+          <t>L92: stray/suspicious non-ASCII glyph(s): U+56FD CJK UNIFIED IDEOGRAPH-56FD | isolated marker/symbol line :: 国</t>
+        </is>
+      </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L58: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: 1st Decemberâ€™</t>
+          <t>L41: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | abbreviation/spacing may be garbled :: E.F. • &gt;</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -685,7 +697,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L56: symbol-only separator/garbage line :: 1850.</t>
+          <t>L49: isolated marker/symbol line :: P</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -701,7 +713,7 @@
       </c>
       <c r="W3" s="1" t="inlineStr">
         <is>
-          <t>L95: abbreviation/spacing may be garbled :: A.B.in theÂ§</t>
+          <t>L95: abbreviation/spacing may be garbled :: A.B.in the§</t>
         </is>
       </c>
       <c r="X3" s="1" t="inlineStr"/>
@@ -732,7 +744,7 @@
       <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L98: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Letter,â€”,</t>
+          <t>L121: stray/suspicious non-ASCII glyph(s): U+25A0 BLACK SQUARE | isolated marker/symbol line :: ■</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -744,7 +756,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L59: symbol-only separator/garbage line :: 1849.</t>
+          <t>L56: symbol-only separator/garbage line :: 1850.</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -770,12 +782,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -790,12 +802,12 @@
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L67: isolated marker/symbol line :: 0</t>
+          <t>L54: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA | isolated marker/symbol line :: r ，</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L63: isolated marker/symbol line :: 5</t>
+          <t>L59: symbol-only separator/garbage line :: 1849.</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
@@ -837,12 +849,12 @@
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L69: symbol-only separator/garbage line :: 1850.</t>
+          <t>L67: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L103: symbol-only separator/garbage line :: 1850.</t>
+          <t>L63: isolated marker/symbol line :: 5</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr"/>
@@ -884,12 +896,12 @@
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L74: symbol-only separator/garbage line :: 1850.</t>
+          <t>L69: symbol-only separator/garbage line :: 1850.</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L121: isolated marker/symbol line :: â–</t>
+          <t>L103: symbol-only separator/garbage line :: 1850.</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
@@ -931,12 +943,12 @@
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L81: symbol-only separator/garbage line :: 1850.</t>
+          <t>L74: symbol-only separator/garbage line :: 1850.</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L124: symbol-only separator/garbage line :: 1850.</t>
+          <t>L121: stray/suspicious non-ASCII glyph(s): U+25A0 BLACK SQUARE | isolated marker/symbol line :: ■</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
@@ -978,12 +990,12 @@
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L86: isolated marker/symbol line :: 1</t>
+          <t>L81: symbol-only separator/garbage line :: 1850.</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>L126: isolated marker/symbol line :: R.</t>
+          <t>L124: symbol-only separator/garbage line :: 1850.</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr"/>
@@ -1005,7 +1017,7 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
@@ -1025,12 +1037,12 @@
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L90: symbol-only separator/garbage line :: 1800.</t>
+          <t>L86: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>L130: symbol-only separator/garbage line :: 1800.</t>
+          <t>L126: isolated marker/symbol line :: R.</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr"/>
@@ -1057,7 +1069,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1072,10 +1084,14 @@
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L96: isolated marker/symbol line :: R.</t>
-        </is>
-      </c>
-      <c r="O11" s="1" t="inlineStr"/>
+          <t>L90: symbol-only separator/garbage line :: 1800.</t>
+        </is>
+      </c>
+      <c r="O11" s="1" t="inlineStr">
+        <is>
+          <t>L130: symbol-only separator/garbage line :: 1800.</t>
+        </is>
+      </c>
       <c r="P11" s="1" t="inlineStr"/>
       <c r="Q11" s="1" t="inlineStr"/>
       <c r="R11" s="1" t="inlineStr"/>
@@ -1095,12 +1111,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1113,7 +1129,11 @@
       <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
-      <c r="N12" s="1" t="inlineStr"/>
+      <c r="N12" s="1" t="inlineStr">
+        <is>
+          <t>L92: stray/suspicious non-ASCII glyph(s): U+56FD CJK UNIFIED IDEOGRAPH-56FD | isolated marker/symbol line :: 国</t>
+        </is>
+      </c>
       <c r="O12" s="1" t="inlineStr"/>
       <c r="P12" s="1" t="inlineStr"/>
       <c r="Q12" s="1" t="inlineStr"/>
@@ -1152,7 +1172,11 @@
       <c r="K13" s="1" t="inlineStr"/>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
-      <c r="N13" s="1" t="inlineStr"/>
+      <c r="N13" s="1" t="inlineStr">
+        <is>
+          <t>L96: isolated marker/symbol line :: R.</t>
+        </is>
+      </c>
       <c r="O13" s="1" t="inlineStr"/>
       <c r="P13" s="1" t="inlineStr"/>
       <c r="Q13" s="1" t="inlineStr"/>
